--- a/PFP-C/Input data and Generated Schedule/9.xlsx
+++ b/PFP-C/Input data and Generated Schedule/9.xlsx
@@ -32807,7 +32807,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32832,7 +32832,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>objective all vehicle travel individually</t>
+          <t>objective_all_vehicle_travel_individually</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -32842,7 +32842,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>objective LLA</t>
+          <t>objective_LLA</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -32852,11 +32852,131 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>objective lb</t>
+          <t>objective_lb</t>
         </is>
       </c>
       <c r="B5" t="n">
         <v>40.26000000000001</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_5</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_5</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_10</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_10</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_15</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_15</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_20</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_20</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_25</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_25</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>max_charge_30</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>mean_charge_30</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -43350,7 +43470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43386,25 +43506,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Saving_time_(minute)</t>
+          <t>Saving_time(%)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time(%)</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Exit</t>
         </is>
@@ -43437,18 +43552,15 @@
         <v>5.898734177215192</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>344.7484984984985</v>
       </c>
       <c r="I2" t="n">
-        <v>344.7484984984985</v>
+        <v>3.498498498498499</v>
       </c>
       <c r="J2" t="n">
-        <v>3.498498498498499</v>
-      </c>
-      <c r="K2" t="n">
         <v>1.01479731274703</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43481,18 +43593,15 @@
         <v>5.40540540540541</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>149.710960960961</v>
       </c>
       <c r="I3" t="n">
-        <v>149.710960960961</v>
+        <v>1.501501501501503</v>
       </c>
       <c r="J3" t="n">
-        <v>1.501501501501503</v>
-      </c>
-      <c r="K3" t="n">
         <v>1.002933580723617</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -43525,18 +43634,15 @@
         <v>5.459459459459458</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>162.3235735735736</v>
       </c>
       <c r="I4" t="n">
-        <v>162.3235735735736</v>
+        <v>1.516516516516516</v>
       </c>
       <c r="J4" t="n">
-        <v>1.516516516516516</v>
-      </c>
-      <c r="K4" t="n">
         <v>0.9342552551858098</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -43569,18 +43675,15 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>305.7402402402403</v>
       </c>
       <c r="I5" t="n">
-        <v>305.7402402402403</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43613,18 +43716,15 @@
         <v>5.508474576271182</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>300.6351351351351</v>
       </c>
       <c r="I6" t="n">
-        <v>300.6351351351351</v>
+        <v>2.927927927927925</v>
       </c>
       <c r="J6" t="n">
-        <v>2.927927927927925</v>
-      </c>
-      <c r="K6" t="n">
         <v>0.9739140857943385</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43657,18 +43757,15 @@
         <v>5.364238410596024</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>254.427927927928</v>
       </c>
       <c r="I7" t="n">
-        <v>254.427927927928</v>
+        <v>2.432432432432431</v>
       </c>
       <c r="J7" t="n">
-        <v>2.432432432432431</v>
-      </c>
-      <c r="K7" t="n">
         <v>0.9560398704034837</v>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -43701,18 +43798,15 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>197.1118618618619</v>
       </c>
       <c r="I8" t="n">
-        <v>197.1118618618619</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -43745,18 +43839,15 @@
         <v>4.540540540540544</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>170.4316816816817</v>
       </c>
       <c r="I9" t="n">
-        <v>170.4316816816817</v>
+        <v>1.261261261261262</v>
       </c>
       <c r="J9" t="n">
-        <v>1.261261261261262</v>
-      </c>
-      <c r="K9" t="n">
         <v>0.740039204457856</v>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -43789,18 +43880,15 @@
         <v>4.101265822784808</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>345.6493993993994</v>
       </c>
       <c r="I10" t="n">
-        <v>345.6493993993994</v>
+        <v>2.432432432432431</v>
       </c>
       <c r="J10" t="n">
-        <v>2.432432432432431</v>
-      </c>
-      <c r="K10" t="n">
         <v>0.7037282392676011</v>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43833,18 +43921,15 @@
         <v>5.139240506329109</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>326.7304804804805</v>
       </c>
       <c r="I11" t="n">
-        <v>326.7304804804805</v>
+        <v>3.048048048048046</v>
       </c>
       <c r="J11" t="n">
-        <v>3.048048048048046</v>
-      </c>
-      <c r="K11" t="n">
         <v>0.9328936937764953</v>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -43877,18 +43962,15 @@
         <v>7.891891891891886</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>178.5397897897898</v>
       </c>
       <c r="I12" t="n">
-        <v>178.5397897897898</v>
+        <v>2.192192192192191</v>
       </c>
       <c r="J12" t="n">
-        <v>2.192192192192191</v>
-      </c>
-      <c r="K12" t="n">
         <v>1.227845173769526</v>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -43921,18 +44003,15 @@
         <v>4.618736383442279</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>393.0487987987988</v>
       </c>
       <c r="I13" t="n">
-        <v>393.0487987987988</v>
+        <v>3.183183183183192</v>
       </c>
       <c r="J13" t="n">
-        <v>3.183183183183192</v>
-      </c>
-      <c r="K13" t="n">
         <v>0.8098697141198135</v>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -43965,18 +44044,15 @@
         <v>6.208053691275155</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>274.2507507507507</v>
       </c>
       <c r="I14" t="n">
-        <v>274.2507507507507</v>
+        <v>2.777777777777771</v>
       </c>
       <c r="J14" t="n">
-        <v>2.777777777777771</v>
-      </c>
-      <c r="K14" t="n">
         <v>1.012860592058076</v>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -44009,18 +44085,15 @@
         <v>7.302631578947391</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>393.051051051051</v>
       </c>
       <c r="I15" t="n">
-        <v>393.051051051051</v>
+        <v>5.000000000000016</v>
       </c>
       <c r="J15" t="n">
-        <v>5.000000000000016</v>
-      </c>
-      <c r="K15" t="n">
         <v>1.272099384196939</v>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -44053,18 +44126,15 @@
         <v>8.178807947019864</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>260.7342342342342</v>
       </c>
       <c r="I16" t="n">
-        <v>260.7342342342342</v>
+        <v>3.708708708708707</v>
       </c>
       <c r="J16" t="n">
-        <v>3.708708708708707</v>
-      </c>
-      <c r="K16" t="n">
         <v>1.422409573334715</v>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -44097,18 +44167,15 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>354.9519519519521</v>
       </c>
       <c r="I17" t="n">
-        <v>354.9519519519521</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -44141,18 +44208,15 @@
         <v>8.300000000000017</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>435.6606606606607</v>
       </c>
       <c r="I18" t="n">
-        <v>435.6606606606607</v>
+        <v>6.231231231231244</v>
       </c>
       <c r="J18" t="n">
-        <v>6.231231231231244</v>
-      </c>
-      <c r="K18" t="n">
         <v>1.43029467516802</v>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -44185,18 +44249,15 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>158.4196696696697</v>
       </c>
       <c r="I19" t="n">
-        <v>158.4196696696697</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>p7</t>
         </is>
@@ -44229,18 +44290,15 @@
         <v>9.999999999999986</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>197.1193693693693</v>
       </c>
       <c r="I20" t="n">
-        <v>197.1193693693693</v>
+        <v>3.558558558558553</v>
       </c>
       <c r="J20" t="n">
-        <v>3.558558558558553</v>
-      </c>
-      <c r="K20" t="n">
         <v>1.805281018269898</v>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -44273,18 +44331,15 @@
         <v>9.100877192982475</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>388.5465465465466</v>
       </c>
       <c r="I21" t="n">
-        <v>388.5465465465466</v>
+        <v>6.231231231231244</v>
       </c>
       <c r="J21" t="n">
-        <v>6.231231231231244</v>
-      </c>
-      <c r="K21" t="n">
         <v>1.603728378649934</v>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -44317,18 +44372,15 @@
         <v>7.807017543859665</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>406.2642642642642</v>
       </c>
       <c r="I22" t="n">
-        <v>406.2642642642642</v>
+        <v>5.345345345345356</v>
       </c>
       <c r="J22" t="n">
-        <v>5.345345345345356</v>
-      </c>
-      <c r="K22" t="n">
         <v>1.315731117780113</v>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -44361,18 +44413,15 @@
         <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>359.7567567567568</v>
       </c>
       <c r="I23" t="n">
-        <v>359.7567567567568</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -44405,18 +44454,15 @@
         <v>3.544303797468357</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>203.1253753753754</v>
       </c>
       <c r="I24" t="n">
-        <v>203.1253753753754</v>
+        <v>1.261261261261262</v>
       </c>
       <c r="J24" t="n">
-        <v>1.261261261261262</v>
-      </c>
-      <c r="K24" t="n">
         <v>0.6209274734535031</v>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>p8</t>
         </is>
@@ -44449,18 +44495,15 @@
         <v>5.38126361655775</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>393.9496996996997</v>
       </c>
       <c r="I25" t="n">
-        <v>393.9496996996997</v>
+        <v>3.70870870870872</v>
       </c>
       <c r="J25" t="n">
-        <v>3.70870870870872</v>
-      </c>
-      <c r="K25" t="n">
         <v>0.9414168132469189</v>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>p10</t>
         </is>
@@ -44493,18 +44536,15 @@
         <v>8.662280701754394</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>401.7597597597598</v>
       </c>
       <c r="I26" t="n">
-        <v>401.7597597597598</v>
+        <v>5.930930930930938</v>
       </c>
       <c r="J26" t="n">
-        <v>5.930930930930938</v>
-      </c>
-      <c r="K26" t="n">
         <v>1.476238171408071</v>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>p9</t>
         </is>
@@ -44521,7 +44561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44547,20 +44587,15 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>before_due_time_(minute)</t>
+          <t>duration_trip_alone_(minute)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>duration_trip_alone_(minute)</t>
+          <t>Saving_time_(minute)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Saving_time_(minute)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Saving_time(%)</t>
         </is>
@@ -44593,9 +44628,6 @@
       <c r="H2" t="n">
         <v>25</v>
       </c>
-      <c r="I2" t="n">
-        <v>25</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -44616,15 +44648,12 @@
         <v>5.136528929752037</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>294.2675375375375</v>
       </c>
       <c r="G3" t="n">
-        <v>294.2675375375375</v>
+        <v>2.709909909909912</v>
       </c>
       <c r="H3" t="n">
-        <v>2.709909909909912</v>
-      </c>
-      <c r="I3" t="n">
         <v>0.8878921331124704</v>
       </c>
     </row>
@@ -44647,15 +44676,12 @@
         <v>3.087505648348876</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>94.11908187938599</v>
       </c>
       <c r="G4" t="n">
-        <v>94.11908187938599</v>
+        <v>1.9928396443986</v>
       </c>
       <c r="H4" t="n">
-        <v>1.9928396443986</v>
-      </c>
-      <c r="I4" t="n">
         <v>0.5348383922609713</v>
       </c>
     </row>
@@ -44678,15 +44704,12 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>149.710960960961</v>
       </c>
       <c r="G5" t="n">
-        <v>149.710960960961</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -44709,15 +44732,12 @@
         <v>4.101265822784808</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>197.1193693693693</v>
       </c>
       <c r="G6" t="n">
-        <v>197.1193693693693</v>
+        <v>1.261261261261262</v>
       </c>
       <c r="H6" t="n">
-        <v>1.261261261261262</v>
-      </c>
-      <c r="I6" t="n">
         <v>0.7037282392676011</v>
       </c>
     </row>
@@ -44740,15 +44760,12 @@
         <v>5.40540540540541</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>305.7402402402403</v>
       </c>
       <c r="G7" t="n">
-        <v>305.7402402402403</v>
+        <v>2.777777777777771</v>
       </c>
       <c r="H7" t="n">
-        <v>2.777777777777771</v>
-      </c>
-      <c r="I7" t="n">
         <v>0.9560398704034837</v>
       </c>
     </row>
@@ -44771,15 +44788,12 @@
         <v>7.807017543859665</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>388.5465465465466</v>
       </c>
       <c r="G8" t="n">
-        <v>388.5465465465466</v>
+        <v>3.708708708708707</v>
       </c>
       <c r="H8" t="n">
-        <v>3.708708708708707</v>
-      </c>
-      <c r="I8" t="n">
         <v>1.272099384196939</v>
       </c>
     </row>
@@ -44802,15 +44816,12 @@
         <v>9.999999999999986</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>435.6606606606607</v>
       </c>
       <c r="G9" t="n">
-        <v>435.6606606606607</v>
+        <v>6.231231231231244</v>
       </c>
       <c r="H9" t="n">
-        <v>6.231231231231244</v>
-      </c>
-      <c r="I9" t="n">
         <v>1.805281018269898</v>
       </c>
     </row>
